--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G890"/>
+  <dimension ref="A1:G891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24466,6 +24466,33 @@
         <v>214.19</v>
       </c>
       <c r="G890" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>232.63</v>
+      </c>
+      <c r="C891" t="n">
+        <v>227.48</v>
+      </c>
+      <c r="D891" t="n">
+        <v>223.71</v>
+      </c>
+      <c r="E891" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="F891" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="G891" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24482,7 +24509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B943"/>
+  <dimension ref="A1:B944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33915,6 +33942,16 @@
       </c>
       <c r="B943" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -34077,28 +34114,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3051208067118404</v>
+        <v>-0.3067746346550856</v>
       </c>
       <c r="J2" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K2" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02664477057244063</v>
+        <v>0.02698785427001049</v>
       </c>
       <c r="M2" t="n">
-        <v>10.76380595481159</v>
+        <v>10.7602913277635</v>
       </c>
       <c r="N2" t="n">
-        <v>186.8588148297926</v>
+        <v>186.7057886936513</v>
       </c>
       <c r="O2" t="n">
-        <v>13.66963111535174</v>
+        <v>13.66403266585862</v>
       </c>
       <c r="P2" t="n">
-        <v>247.7751391940731</v>
+        <v>247.791779838809</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34149,28 +34186,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1610092835874977</v>
+        <v>0.1611063229888867</v>
       </c>
       <c r="J3" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K3" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03683167736356552</v>
+        <v>0.03696814640211044</v>
       </c>
       <c r="M3" t="n">
-        <v>4.60743461625322</v>
+        <v>4.602718036840107</v>
       </c>
       <c r="N3" t="n">
-        <v>37.24715352185292</v>
+        <v>37.20549877956237</v>
       </c>
       <c r="O3" t="n">
-        <v>6.103044610835884</v>
+        <v>6.099631036346573</v>
       </c>
       <c r="P3" t="n">
-        <v>222.8312425936956</v>
+        <v>222.8302661933327</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34221,28 +34258,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4740430530327152</v>
+        <v>0.4738786444599405</v>
       </c>
       <c r="J4" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K4" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3823711269030791</v>
+        <v>0.3828242601793077</v>
       </c>
       <c r="M4" t="n">
-        <v>3.247974046614032</v>
+        <v>3.245140546446094</v>
       </c>
       <c r="N4" t="n">
-        <v>19.94291475939221</v>
+        <v>19.92106957876299</v>
       </c>
       <c r="O4" t="n">
-        <v>4.465749070356753</v>
+        <v>4.463302541701939</v>
       </c>
       <c r="P4" t="n">
-        <v>211.9637747749386</v>
+        <v>211.9654290368963</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34293,28 +34330,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5893032380111372</v>
+        <v>0.5891734920191972</v>
       </c>
       <c r="J5" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K5" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5085486972537957</v>
+        <v>0.509093750572027</v>
       </c>
       <c r="M5" t="n">
-        <v>3.464007448878402</v>
+        <v>3.460797458325558</v>
       </c>
       <c r="N5" t="n">
-        <v>18.43894886581795</v>
+        <v>18.41858131826381</v>
       </c>
       <c r="O5" t="n">
-        <v>4.294059718473644</v>
+        <v>4.291687467449583</v>
       </c>
       <c r="P5" t="n">
-        <v>203.3846912327278</v>
+        <v>203.3859967234027</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34365,28 +34402,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5938958461901275</v>
+        <v>0.593594749991698</v>
       </c>
       <c r="J6" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="K6" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5710081232999968</v>
+        <v>0.5713746229397891</v>
       </c>
       <c r="M6" t="n">
-        <v>2.990362127421267</v>
+        <v>2.988556823996901</v>
       </c>
       <c r="N6" t="n">
-        <v>14.55921361246089</v>
+        <v>14.54474186196984</v>
       </c>
       <c r="O6" t="n">
-        <v>3.81565375950975</v>
+        <v>3.813756922244762</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2040532996139</v>
+        <v>200.2070828982429</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34424,7 +34461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G890"/>
+  <dimension ref="A1:G891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67357,6 +67394,43 @@
         </is>
       </c>
     </row>
+    <row r="891">
+      <c r="A891" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>-40.94753103755185,173.04983707976913</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>-40.94684809296953,173.04969248570862</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>-40.946146841784724,173.04968254278018</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>-40.94544118421063,173.04974302409292</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>-40.9447817378544,173.04996546290548</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G891"/>
+  <dimension ref="A1:G892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24493,6 +24493,33 @@
         <v>214.5</v>
       </c>
       <c r="G891" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>231.59</v>
+      </c>
+      <c r="C892" t="n">
+        <v>226.81</v>
+      </c>
+      <c r="D892" t="n">
+        <v>223.23</v>
+      </c>
+      <c r="E892" t="n">
+        <v>217.89</v>
+      </c>
+      <c r="F892" t="n">
+        <v>215.47</v>
+      </c>
+      <c r="G892" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24509,7 +24536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B944"/>
+  <dimension ref="A1:B945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33952,6 +33979,16 @@
       </c>
       <c r="B944" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -34114,28 +34151,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3067746346550856</v>
+        <v>-0.3086600016567088</v>
       </c>
       <c r="J2" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K2" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02698785427001049</v>
+        <v>0.02737138745627465</v>
       </c>
       <c r="M2" t="n">
-        <v>10.7602913277635</v>
+        <v>10.75796325530789</v>
       </c>
       <c r="N2" t="n">
-        <v>186.7057886936513</v>
+        <v>186.5701305400711</v>
       </c>
       <c r="O2" t="n">
-        <v>13.66403266585862</v>
+        <v>13.65906770391271</v>
       </c>
       <c r="P2" t="n">
-        <v>247.791779838809</v>
+        <v>247.8107853026157</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34186,28 +34223,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1611063229888867</v>
+        <v>0.1610472420693899</v>
       </c>
       <c r="J3" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K3" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03696814640211044</v>
+        <v>0.03703628383948843</v>
       </c>
       <c r="M3" t="n">
-        <v>4.602718036840107</v>
+        <v>4.597843030748089</v>
       </c>
       <c r="N3" t="n">
-        <v>37.20549877956237</v>
+        <v>37.16381432307043</v>
       </c>
       <c r="O3" t="n">
-        <v>6.099631036346573</v>
+        <v>6.096213113324568</v>
       </c>
       <c r="P3" t="n">
-        <v>222.8302661933327</v>
+        <v>222.8308617592232</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34258,28 +34295,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4738786444599405</v>
+        <v>0.4735998146860167</v>
       </c>
       <c r="J4" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K4" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3828242601793077</v>
+        <v>0.3831525795368963</v>
       </c>
       <c r="M4" t="n">
-        <v>3.245140546446094</v>
+        <v>3.242880512279519</v>
       </c>
       <c r="N4" t="n">
-        <v>19.92106957876299</v>
+        <v>19.90032755091899</v>
       </c>
       <c r="O4" t="n">
-        <v>4.463302541701939</v>
+        <v>4.460978317692094</v>
       </c>
       <c r="P4" t="n">
-        <v>211.9654290368963</v>
+        <v>211.9682397836485</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34330,28 +34367,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5891734920191972</v>
+        <v>0.5889424981751201</v>
       </c>
       <c r="J5" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K5" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L5" t="n">
-        <v>0.509093750572027</v>
+        <v>0.5095443836762478</v>
       </c>
       <c r="M5" t="n">
-        <v>3.460797458325558</v>
+        <v>3.45812233290046</v>
       </c>
       <c r="N5" t="n">
-        <v>18.41858131826381</v>
+        <v>18.39901864381536</v>
       </c>
       <c r="O5" t="n">
-        <v>4.291687467449583</v>
+        <v>4.289407726460072</v>
       </c>
       <c r="P5" t="n">
-        <v>203.3859967234027</v>
+        <v>203.3883252595123</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34402,28 +34439,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.593594749991698</v>
+        <v>0.5935125601650737</v>
       </c>
       <c r="J6" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K6" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5713746229397891</v>
+        <v>0.5719527765808874</v>
       </c>
       <c r="M6" t="n">
-        <v>2.988556823996901</v>
+        <v>2.985625296100745</v>
       </c>
       <c r="N6" t="n">
-        <v>14.54474186196984</v>
+        <v>14.52855821391315</v>
       </c>
       <c r="O6" t="n">
-        <v>3.813756922244762</v>
+        <v>3.81163458556997</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2070828982429</v>
+        <v>200.2079114137383</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34461,7 +34498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G891"/>
+  <dimension ref="A1:G892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67431,6 +67468,43 @@
         </is>
       </c>
     </row>
+    <row r="892">
+      <c r="A892" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>-40.94753212004017,173.04982480631648</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>-40.94684809358996,173.04968452554033</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>-40.9461464728176,173.0496768608328</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>-40.94544059387598,173.04973821567154</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>-40.94478513330923,173.04997608134283</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G892"/>
+  <dimension ref="A1:G895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24520,6 +24520,87 @@
         <v>215.47</v>
       </c>
       <c r="G892" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:05+00:00</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>230.75</v>
+      </c>
+      <c r="C893" t="n">
+        <v>225.73</v>
+      </c>
+      <c r="D893" t="n">
+        <v>223.15</v>
+      </c>
+      <c r="E893" t="n">
+        <v>216.91</v>
+      </c>
+      <c r="F893" t="n">
+        <v>215.35</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>230.55</v>
+      </c>
+      <c r="C894" t="n">
+        <v>225.59</v>
+      </c>
+      <c r="D894" t="n">
+        <v>223.06</v>
+      </c>
+      <c r="E894" t="n">
+        <v>216.93</v>
+      </c>
+      <c r="F894" t="n">
+        <v>215.35</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>231.67</v>
+      </c>
+      <c r="C895" t="n">
+        <v>225.97</v>
+      </c>
+      <c r="D895" t="n">
+        <v>222.74</v>
+      </c>
+      <c r="E895" t="n">
+        <v>216.97</v>
+      </c>
+      <c r="F895" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="G895" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24536,7 +24617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B945"/>
+  <dimension ref="A1:B948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33989,6 +34070,36 @@
       </c>
       <c r="B945" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
@@ -34151,28 +34262,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3086600016567088</v>
+        <v>-0.3146644316632837</v>
       </c>
       <c r="J2" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="K2" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02737138745627465</v>
+        <v>0.02859879105075513</v>
       </c>
       <c r="M2" t="n">
-        <v>10.75796325530789</v>
+        <v>10.75305566054049</v>
       </c>
       <c r="N2" t="n">
-        <v>186.5701305400711</v>
+        <v>186.1951352848724</v>
       </c>
       <c r="O2" t="n">
-        <v>13.65906770391271</v>
+        <v>13.6453338282679</v>
       </c>
       <c r="P2" t="n">
-        <v>247.8107853026157</v>
+        <v>247.8714563221319</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34223,28 +34334,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1610472420693899</v>
+        <v>0.1601401934505303</v>
       </c>
       <c r="J3" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="K3" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03703628383948843</v>
+        <v>0.03691140671455884</v>
       </c>
       <c r="M3" t="n">
-        <v>4.597843030748089</v>
+        <v>4.58684141872118</v>
       </c>
       <c r="N3" t="n">
-        <v>37.16381432307043</v>
+        <v>37.04489731935674</v>
       </c>
       <c r="O3" t="n">
-        <v>6.096213113324568</v>
+        <v>6.086451948332192</v>
       </c>
       <c r="P3" t="n">
-        <v>222.8308617592232</v>
+        <v>222.8400267100225</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34295,28 +34406,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4735998146860167</v>
+        <v>0.4725831766429055</v>
       </c>
       <c r="J4" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="K4" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3831525795368963</v>
+        <v>0.3839281966379845</v>
       </c>
       <c r="M4" t="n">
-        <v>3.242880512279519</v>
+        <v>3.237013952388694</v>
       </c>
       <c r="N4" t="n">
-        <v>19.90032755091899</v>
+        <v>19.84083260890558</v>
       </c>
       <c r="O4" t="n">
-        <v>4.460978317692094</v>
+        <v>4.454304952392189</v>
       </c>
       <c r="P4" t="n">
-        <v>211.9682397836485</v>
+        <v>211.9785140798157</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34367,28 +34478,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5889424981751201</v>
+        <v>0.5875714677847014</v>
       </c>
       <c r="J5" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="K5" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5095443836762478</v>
+        <v>0.5101873720528597</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45812233290046</v>
+        <v>3.453638608080668</v>
       </c>
       <c r="N5" t="n">
-        <v>18.39901864381536</v>
+        <v>18.35032350034901</v>
       </c>
       <c r="O5" t="n">
-        <v>4.289407726460072</v>
+        <v>4.283727757496852</v>
       </c>
       <c r="P5" t="n">
-        <v>203.3883252595123</v>
+        <v>203.4021792100515</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34439,28 +34550,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5935125601650737</v>
+        <v>0.5933579906739158</v>
       </c>
       <c r="J6" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="K6" t="n">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5719527765808874</v>
+        <v>0.5737581316259679</v>
       </c>
       <c r="M6" t="n">
-        <v>2.985625296100745</v>
+        <v>2.97713068480187</v>
       </c>
       <c r="N6" t="n">
-        <v>14.52855821391315</v>
+        <v>14.48047803309804</v>
       </c>
       <c r="O6" t="n">
-        <v>3.81163458556997</v>
+        <v>3.805322329724257</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2079114137383</v>
+        <v>200.2094709159184</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34498,7 +34609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G892"/>
+  <dimension ref="A1:G895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67505,6 +67616,117 @@
         </is>
       </c>
     </row>
+    <row r="893">
+      <c r="A893" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:05+00:00</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>-40.947532994356706,173.04981489314287</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>-40.9468480945889,173.04967169422426</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>-40.94614641132304,173.04967591384155</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>-40.94543918283137,173.04972672237196</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>-40.94478471325302,173.04997476772166</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:18+00:00</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>-40.947533202527175,173.0498125328634</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>-40.94684809471829,173.04967003090553</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>-40.946146342141674,173.04967484847646</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>-40.945439211628205,173.0497269569291</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>-40.94478471325302,173.04997476772166</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>-40.94753203677188,173.04982575042823</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>-40.94684809436704,173.04967454562782</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>-40.94614609616337,173.0496710605116</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>-40.945439269221886,173.04972742604335</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>-40.9447876886509,173.0499840725387</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G895"/>
+  <dimension ref="A1:G899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24601,6 +24601,114 @@
         <v>216.2</v>
       </c>
       <c r="G895" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>231.57</v>
+      </c>
+      <c r="C896" t="n">
+        <v>224.95</v>
+      </c>
+      <c r="D896" t="n">
+        <v>221.97</v>
+      </c>
+      <c r="E896" t="n">
+        <v>216.43</v>
+      </c>
+      <c r="F896" t="n">
+        <v>215.62</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:13:14+00:00</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>233.42</v>
+      </c>
+      <c r="C897" t="n">
+        <v>223.64</v>
+      </c>
+      <c r="D897" t="n">
+        <v>221.35</v>
+      </c>
+      <c r="E897" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="F897" t="n">
+        <v>215.98</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>236.12</v>
+      </c>
+      <c r="C898" t="n">
+        <v>223.54</v>
+      </c>
+      <c r="D898" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="E898" t="n">
+        <v>215.69</v>
+      </c>
+      <c r="F898" t="n">
+        <v>216.11</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>237.55</v>
+      </c>
+      <c r="C899" t="n">
+        <v>223.84</v>
+      </c>
+      <c r="D899" t="n">
+        <v>221.56</v>
+      </c>
+      <c r="E899" t="n">
+        <v>215.76</v>
+      </c>
+      <c r="F899" t="n">
+        <v>216.46</v>
+      </c>
+      <c r="G899" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24617,7 +24725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B948"/>
+  <dimension ref="A1:B952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34100,6 +34208,46 @@
       </c>
       <c r="B948" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>1.69</v>
       </c>
     </row>
   </sheetData>
@@ -34262,28 +34410,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3146644316632837</v>
+        <v>-0.319128818542611</v>
       </c>
       <c r="J2" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="K2" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02859879105075513</v>
+        <v>0.02967533876410855</v>
       </c>
       <c r="M2" t="n">
-        <v>10.75305566054049</v>
+        <v>10.72824351590369</v>
       </c>
       <c r="N2" t="n">
-        <v>186.1951352848724</v>
+        <v>185.4944875508382</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6453338282679</v>
+        <v>13.61963610199767</v>
       </c>
       <c r="P2" t="n">
-        <v>247.8714563221319</v>
+        <v>247.9167173909487</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34334,28 +34482,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1601401934505303</v>
+        <v>0.1573170019994552</v>
       </c>
       <c r="J3" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="K3" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03691140671455884</v>
+        <v>0.0359924918047495</v>
       </c>
       <c r="M3" t="n">
-        <v>4.58684141872118</v>
+        <v>4.580125947232967</v>
       </c>
       <c r="N3" t="n">
-        <v>37.04489731935674</v>
+        <v>36.92303569418525</v>
       </c>
       <c r="O3" t="n">
-        <v>6.086451948332192</v>
+        <v>6.076432809978668</v>
       </c>
       <c r="P3" t="n">
-        <v>222.8400267100225</v>
+        <v>222.868665768302</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34406,28 +34554,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4725831766429055</v>
+        <v>0.4698724701229394</v>
       </c>
       <c r="J4" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="K4" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3839281966379845</v>
+        <v>0.3832443543415145</v>
       </c>
       <c r="M4" t="n">
-        <v>3.237013952388694</v>
+        <v>3.236025697540417</v>
       </c>
       <c r="N4" t="n">
-        <v>19.84083260890558</v>
+        <v>19.79132833888921</v>
       </c>
       <c r="O4" t="n">
-        <v>4.454304952392189</v>
+        <v>4.448744580091018</v>
       </c>
       <c r="P4" t="n">
-        <v>211.9785140798157</v>
+        <v>212.0060097782714</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34478,28 +34626,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5875714677847014</v>
+        <v>0.5846644583347023</v>
       </c>
       <c r="J5" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="K5" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5101873720528597</v>
+        <v>0.5097354565141872</v>
       </c>
       <c r="M5" t="n">
-        <v>3.453638608080668</v>
+        <v>3.453179846036893</v>
       </c>
       <c r="N5" t="n">
-        <v>18.35032350034901</v>
+        <v>18.3137214893809</v>
       </c>
       <c r="O5" t="n">
-        <v>4.283727757496852</v>
+        <v>4.279453410119205</v>
       </c>
       <c r="P5" t="n">
-        <v>203.4021792100515</v>
+        <v>203.4316668625988</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34550,28 +34698,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5933579906739158</v>
+        <v>0.5934822012492773</v>
       </c>
       <c r="J6" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="K6" t="n">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5737581316259679</v>
+        <v>0.5764379240695757</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97713068480187</v>
+        <v>2.965020430949448</v>
       </c>
       <c r="N6" t="n">
-        <v>14.48047803309804</v>
+        <v>14.41642230055825</v>
       </c>
       <c r="O6" t="n">
-        <v>3.805322329724257</v>
+        <v>3.79689640371689</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2094709159184</v>
+        <v>200.2082085165252</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34609,7 +34757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G895"/>
+  <dimension ref="A1:G899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67727,6 +67875,154 @@
         </is>
       </c>
     </row>
+    <row r="896">
+      <c r="A896" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>-40.94753214085724,173.04982457028854</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>-40.946848095309484,173.04966242716267</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>-40.94614550427755,173.04966194572125</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>-40.94543849170706,173.0497210930009</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>-40.94478565837947,173.04997772336932</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:13:14+00:00</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>-40.94753021527622,173.04984640287233</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>-40.946848096517996,173.04964686325152</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>-40.94614502769364,173.04965460653955</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>-40.94543672069976,173.04970666773812</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>-40.94478691854799,173.04998166423306</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>-40.94752740496136,173.049878266641</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>-40.94684809661016,173.04964567516672</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>-40.946144912391006,173.04965283093108</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>-40.94543742622321,173.04971241438744</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>-40.9447873736088,173.04998308732274</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>-40.947525916531774,173.04989514263593</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>-40.94684809633362,173.04964923942117</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>-40.94614518911727,173.04965709239139</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>-40.945437527012245,173.04971323533738</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>-40.94478859877244,173.0499869187182</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G899"/>
+  <dimension ref="A1:G903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24709,6 +24709,114 @@
         <v>216.46</v>
       </c>
       <c r="G899" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>238.23</v>
+      </c>
+      <c r="C900" t="n">
+        <v>223.75</v>
+      </c>
+      <c r="D900" t="n">
+        <v>221.69</v>
+      </c>
+      <c r="E900" t="n">
+        <v>215.68</v>
+      </c>
+      <c r="F900" t="n">
+        <v>216.54</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="C901" t="n">
+        <v>224.04</v>
+      </c>
+      <c r="D901" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="E901" t="n">
+        <v>216.27</v>
+      </c>
+      <c r="F901" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="C902" t="n">
+        <v>223.98</v>
+      </c>
+      <c r="D902" t="n">
+        <v>221.69</v>
+      </c>
+      <c r="E902" t="n">
+        <v>215.84</v>
+      </c>
+      <c r="F902" t="n">
+        <v>216.35</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="C903" t="n">
+        <v>224.18</v>
+      </c>
+      <c r="D903" t="n">
+        <v>221.81</v>
+      </c>
+      <c r="E903" t="n">
+        <v>216.12</v>
+      </c>
+      <c r="F903" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="G903" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24725,7 +24833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B952"/>
+  <dimension ref="A1:B956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34248,6 +34356,46 @@
       </c>
       <c r="B952" t="n">
         <v>1.69</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -34410,28 +34558,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.319128818542611</v>
+        <v>-0.3198900284149079</v>
       </c>
       <c r="J2" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K2" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02967533876410855</v>
+        <v>0.03011850305462693</v>
       </c>
       <c r="M2" t="n">
-        <v>10.72824351590369</v>
+        <v>10.68456050153579</v>
       </c>
       <c r="N2" t="n">
-        <v>185.4944875508382</v>
+        <v>184.6751826894298</v>
       </c>
       <c r="O2" t="n">
-        <v>13.61963610199767</v>
+        <v>13.58952474111695</v>
       </c>
       <c r="P2" t="n">
-        <v>247.9167173909487</v>
+        <v>247.924465206784</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34482,28 +34630,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1573170019994552</v>
+        <v>0.154537925526194</v>
       </c>
       <c r="J3" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K3" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0359924918047495</v>
+        <v>0.03509345013537823</v>
       </c>
       <c r="M3" t="n">
-        <v>4.580125947232967</v>
+        <v>4.573462982755049</v>
       </c>
       <c r="N3" t="n">
-        <v>36.92303569418525</v>
+        <v>36.80028521836617</v>
       </c>
       <c r="O3" t="n">
-        <v>6.076432809978668</v>
+        <v>6.066323863623354</v>
       </c>
       <c r="P3" t="n">
-        <v>222.868665768302</v>
+        <v>222.8969541086825</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34554,28 +34702,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4698724701229394</v>
+        <v>0.4674167232166778</v>
       </c>
       <c r="J4" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K4" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3832443543415145</v>
+        <v>0.3828738977251918</v>
       </c>
       <c r="M4" t="n">
-        <v>3.236025697540417</v>
+        <v>3.23383316925563</v>
       </c>
       <c r="N4" t="n">
-        <v>19.79132833888921</v>
+        <v>19.73551621119788</v>
       </c>
       <c r="O4" t="n">
-        <v>4.448744580091018</v>
+        <v>4.442467356233231</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0060097782714</v>
+        <v>212.0310077186928</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34626,28 +34774,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5846644583347023</v>
+        <v>0.5819633856880896</v>
       </c>
       <c r="J5" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K5" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5097354565141872</v>
+        <v>0.5095214372591337</v>
       </c>
       <c r="M5" t="n">
-        <v>3.453179846036893</v>
+        <v>3.451620305500492</v>
       </c>
       <c r="N5" t="n">
-        <v>18.3137214893809</v>
+        <v>18.27135409463525</v>
       </c>
       <c r="O5" t="n">
-        <v>4.279453410119205</v>
+        <v>4.274500449717517</v>
       </c>
       <c r="P5" t="n">
-        <v>203.4316668625988</v>
+        <v>203.4591616661959</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34698,28 +34846,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5934822012492773</v>
+        <v>0.5939260023948371</v>
       </c>
       <c r="J6" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K6" t="n">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5764379240695757</v>
+        <v>0.5793538157227024</v>
       </c>
       <c r="M6" t="n">
-        <v>2.965020430949448</v>
+        <v>2.953866505744381</v>
       </c>
       <c r="N6" t="n">
-        <v>14.41642230055825</v>
+        <v>14.3535590993618</v>
       </c>
       <c r="O6" t="n">
-        <v>3.79689640371689</v>
+        <v>3.788609124647434</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2082085165252</v>
+        <v>200.2036909652822</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34757,7 +34905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G899"/>
+  <dimension ref="A1:G903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68023,6 +68171,154 @@
         </is>
       </c>
     </row>
+    <row r="900">
+      <c r="A900" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>-40.947525208746214,173.0499031675843</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>-40.9468480964166,173.04964817014482</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>-40.94614528904616,173.0496586312521</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>-40.94543741182477,173.04971229710887</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>-40.944788878809824,173.04998779446578</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>-40.947524667498044,173.04990930430938</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>-40.9468480961492,173.04965161559082</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>-40.94614545046971,173.04966111710397</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>-40.94543826133223,173.04971921654393</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>-40.94478838874439,173.04998626190755</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>-40.947524667498044,173.04990930430938</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>-40.94684809620453,173.0496509027399</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>-40.94614528904616,173.0496586312521</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>-40.94543764219972,173.04971417356583</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>-40.94478821372101,173.04998571456534</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>-40.947524719541164,173.04990871423968</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>-40.94684809602008,173.04965327890955</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>-40.94614538128819,173.04966005173887</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>-40.94543804535579,173.0497174573655</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>-40.94478873879114,173.04998735659197</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G903"/>
+  <dimension ref="A1:G907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24817,6 +24817,114 @@
         <v>216.5</v>
       </c>
       <c r="G903" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:28+00:00</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>240.71</v>
+      </c>
+      <c r="C904" t="n">
+        <v>223.83</v>
+      </c>
+      <c r="D904" t="n">
+        <v>222.47</v>
+      </c>
+      <c r="E904" t="n">
+        <v>216.59</v>
+      </c>
+      <c r="F904" t="n">
+        <v>216.89</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>241.01</v>
+      </c>
+      <c r="C905" t="n">
+        <v>223.76</v>
+      </c>
+      <c r="D905" t="n">
+        <v>222.53</v>
+      </c>
+      <c r="E905" t="n">
+        <v>215.16</v>
+      </c>
+      <c r="F905" t="n">
+        <v>215.01</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>242.91</v>
+      </c>
+      <c r="C906" t="n">
+        <v>224</v>
+      </c>
+      <c r="D906" t="n">
+        <v>222.56</v>
+      </c>
+      <c r="E906" t="n">
+        <v>215.18</v>
+      </c>
+      <c r="F906" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>242.91</v>
+      </c>
+      <c r="C907" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="D907" t="n">
+        <v>222.47</v>
+      </c>
+      <c r="E907" t="n">
+        <v>215.67</v>
+      </c>
+      <c r="F907" t="n">
+        <v>214.96</v>
+      </c>
+      <c r="G907" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24833,7 +24941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B956"/>
+  <dimension ref="A1:B960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34396,6 +34504,46 @@
       </c>
       <c r="B956" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -34558,28 +34706,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3198900284149079</v>
+        <v>-0.3176562932500338</v>
       </c>
       <c r="J2" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="K2" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03011850305462693</v>
+        <v>0.03001046959549403</v>
       </c>
       <c r="M2" t="n">
-        <v>10.68456050153579</v>
+        <v>10.64763533430878</v>
       </c>
       <c r="N2" t="n">
-        <v>184.6751826894298</v>
+        <v>183.8912299626394</v>
       </c>
       <c r="O2" t="n">
-        <v>13.58952474111695</v>
+        <v>13.56065005678708</v>
       </c>
       <c r="P2" t="n">
-        <v>247.924465206784</v>
+        <v>247.9016404390407</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34630,28 +34778,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.154537925526194</v>
+        <v>0.1517635888918045</v>
       </c>
       <c r="J3" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="K3" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03509345013537823</v>
+        <v>0.0341946269583997</v>
       </c>
       <c r="M3" t="n">
-        <v>4.573462982755049</v>
+        <v>4.566969889774252</v>
       </c>
       <c r="N3" t="n">
-        <v>36.80028521836617</v>
+        <v>36.67910734662432</v>
       </c>
       <c r="O3" t="n">
-        <v>6.066323863623354</v>
+        <v>6.056327876413588</v>
       </c>
       <c r="P3" t="n">
-        <v>222.8969541086825</v>
+        <v>222.9252908231859</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34702,28 +34850,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4674167232166778</v>
+        <v>0.465642764557133</v>
       </c>
       <c r="J4" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="K4" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3828738977251918</v>
+        <v>0.383350952579536</v>
       </c>
       <c r="M4" t="n">
-        <v>3.23383316925563</v>
+        <v>3.228271322413458</v>
       </c>
       <c r="N4" t="n">
-        <v>19.73551621119788</v>
+        <v>19.66523183518201</v>
       </c>
       <c r="O4" t="n">
-        <v>4.442467356233231</v>
+        <v>4.434549789458003</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0310077186928</v>
+        <v>212.0491275776039</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34774,28 +34922,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5819633856880896</v>
+        <v>0.5789858836429049</v>
       </c>
       <c r="J5" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="K5" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5095214372591337</v>
+        <v>0.5089052055260445</v>
       </c>
       <c r="M5" t="n">
-        <v>3.451620305500492</v>
+        <v>3.451483491089006</v>
       </c>
       <c r="N5" t="n">
-        <v>18.27135409463525</v>
+        <v>18.23963832655121</v>
       </c>
       <c r="O5" t="n">
-        <v>4.274500449717517</v>
+        <v>4.270788958325055</v>
       </c>
       <c r="P5" t="n">
-        <v>203.4591616661959</v>
+        <v>203.4895776672292</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34846,28 +34994,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5939260023948371</v>
+        <v>0.5934584273993716</v>
       </c>
       <c r="J6" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="K6" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5793538157227024</v>
+        <v>0.5814523093187003</v>
       </c>
       <c r="M6" t="n">
-        <v>2.953866505744381</v>
+        <v>2.945249032047978</v>
       </c>
       <c r="N6" t="n">
-        <v>14.3535590993618</v>
+        <v>14.29431300479365</v>
       </c>
       <c r="O6" t="n">
-        <v>3.788609124647434</v>
+        <v>3.780782062588857</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2036909652822</v>
+        <v>200.2084729190873</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34905,7 +35053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G903"/>
+  <dimension ref="A1:G907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68319,6 +68467,154 @@
         </is>
       </c>
     </row>
+    <row r="904">
+      <c r="A904" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:28+00:00</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>-40.9475226274059,173.04993243504157</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>-40.94684809634285,173.04964912061268</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>-40.946145888619064,173.04966786441628</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>-40.94543872208186,173.04972296945792</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>-40.94479010397332,173.0499916258614</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>-40.94752231514648,173.04993597545962</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>-40.94684809640738,173.04964828895334</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>-40.94614593474003,173.04966857465965</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>-40.94543666310599,173.0497061986239</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>-40.94478352309366,173.04997104579508</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>-40.94752033750101,173.04995839810658</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>-40.946848096186095,173.04965114035687</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>-40.946145957800496,173.04966892978135</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>-40.94543669190287,173.04970643318103</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>-40.944783978154604,173.04997246888465</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>-40.94752033750101,173.04995839810658</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>-40.94684809604775,173.0496529224841</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>-40.946145888619064,173.04966786441628</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>-40.94543739742634,173.04971217983032</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>-40.94478334807022,173.04997049845295</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G907"/>
+  <dimension ref="A1:G910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24927,6 +24927,87 @@
       <c r="G907" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="C908" t="n">
+        <v>225.03</v>
+      </c>
+      <c r="D908" t="n">
+        <v>223.19</v>
+      </c>
+      <c r="E908" t="n">
+        <v>215.76</v>
+      </c>
+      <c r="F908" t="n">
+        <v>215.65</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="C909" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="D909" t="n">
+        <v>222.64</v>
+      </c>
+      <c r="E909" t="n">
+        <v>215.34</v>
+      </c>
+      <c r="F909" t="n">
+        <v>215.12</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>253.47</v>
+      </c>
+      <c r="C910" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="D910" t="n">
+        <v>223.69</v>
+      </c>
+      <c r="E910" t="n">
+        <v>215.41</v>
+      </c>
+      <c r="F910" t="n">
+        <v>215.43</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24941,7 +25022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B960"/>
+  <dimension ref="A1:B963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34544,6 +34625,36 @@
       </c>
       <c r="B960" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>
@@ -34706,28 +34817,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3176562932500338</v>
+        <v>-0.3102384986398862</v>
       </c>
       <c r="J2" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K2" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03001046959549403</v>
+        <v>0.02882078013950951</v>
       </c>
       <c r="M2" t="n">
-        <v>10.64763533430878</v>
+        <v>10.64627027717643</v>
       </c>
       <c r="N2" t="n">
-        <v>183.8912299626394</v>
+        <v>183.6971715732513</v>
       </c>
       <c r="O2" t="n">
-        <v>13.56065005678708</v>
+        <v>13.55349296577275</v>
       </c>
       <c r="P2" t="n">
-        <v>247.9016404390407</v>
+        <v>247.8256214083437</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34778,28 +34889,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1517635888918045</v>
+        <v>0.1501012432146078</v>
       </c>
       <c r="J3" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K3" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0341946269583997</v>
+        <v>0.03371074137440755</v>
       </c>
       <c r="M3" t="n">
-        <v>4.566969889774252</v>
+        <v>4.560217008574426</v>
       </c>
       <c r="N3" t="n">
-        <v>36.67910734662432</v>
+        <v>36.57841368245414</v>
       </c>
       <c r="O3" t="n">
-        <v>6.056327876413588</v>
+        <v>6.048009067656409</v>
       </c>
       <c r="P3" t="n">
-        <v>222.9252908231859</v>
+        <v>222.9423259125868</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34850,28 +34961,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.465642764557133</v>
+        <v>0.4647635909936153</v>
       </c>
       <c r="J4" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K4" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="L4" t="n">
-        <v>0.383350952579536</v>
+        <v>0.384234845294895</v>
       </c>
       <c r="M4" t="n">
-        <v>3.228271322413458</v>
+        <v>3.221960752048453</v>
       </c>
       <c r="N4" t="n">
-        <v>19.66523183518201</v>
+        <v>19.60649664769216</v>
       </c>
       <c r="O4" t="n">
-        <v>4.434549789458003</v>
+        <v>4.427922385012203</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0491275776039</v>
+        <v>212.0581351259285</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34922,28 +35033,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5789858836429049</v>
+        <v>0.5766662330244419</v>
       </c>
       <c r="J5" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K5" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5089052055260445</v>
+        <v>0.5083220285770691</v>
       </c>
       <c r="M5" t="n">
-        <v>3.451483491089006</v>
+        <v>3.451767923400517</v>
       </c>
       <c r="N5" t="n">
-        <v>18.23963832655121</v>
+        <v>18.21831909798826</v>
       </c>
       <c r="O5" t="n">
-        <v>4.270788958325055</v>
+        <v>4.268292292942022</v>
       </c>
       <c r="P5" t="n">
-        <v>203.4895776672292</v>
+        <v>203.5133470563142</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34994,28 +35105,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5934584273993716</v>
+        <v>0.5930177995363087</v>
       </c>
       <c r="J6" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K6" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5814523093187003</v>
+        <v>0.5829693654751763</v>
       </c>
       <c r="M6" t="n">
-        <v>2.945249032047978</v>
+        <v>2.937822911826214</v>
       </c>
       <c r="N6" t="n">
-        <v>14.29431300479365</v>
+        <v>14.24869609672064</v>
       </c>
       <c r="O6" t="n">
-        <v>3.780782062588857</v>
+        <v>3.774744507476055</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2084729190873</v>
+        <v>200.2129884406901</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35053,7 +35164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G907"/>
+  <dimension ref="A1:G910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68615,6 +68726,117 @@
         </is>
       </c>
     </row>
+    <row r="908">
+      <c r="A908" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>-40.94751493538404,173.05001964733012</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>-40.94684809523561,173.04966337763054</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>-40.94614644207033,173.04967638733717</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>-40.945437527012245,173.04971323533738</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>-40.94478576339354,173.04997805177464</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>-40.94751322834995,173.05003900161063</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>-40.94684809600164,173.04965351652652</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>-40.94614601929511,173.04966987677258</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>-40.94543692227791,173.04970830963794</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>-40.944783908145226,173.04997224994779</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>-40.94750934587618,173.05008302079364</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>-40.94684809591861,173.04965458580287</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>-40.9461468264111,173.04968230603234</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>-40.94543702306698,173.04970913058781</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>-40.9447849932905,173.0499756434691</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G910"/>
+  <dimension ref="A1:G915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25008,6 +25008,141 @@
       <c r="G910" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="C911" t="n">
+        <v>224.47</v>
+      </c>
+      <c r="D911" t="n">
+        <v>224.61</v>
+      </c>
+      <c r="E911" t="n">
+        <v>215.46</v>
+      </c>
+      <c r="F911" t="n">
+        <v>215.04</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>257.07</v>
+      </c>
+      <c r="C912" t="n">
+        <v>225.44</v>
+      </c>
+      <c r="D912" t="n">
+        <v>225.65</v>
+      </c>
+      <c r="E912" t="n">
+        <v>216.15</v>
+      </c>
+      <c r="F912" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>257.17</v>
+      </c>
+      <c r="C913" t="n">
+        <v>225.29</v>
+      </c>
+      <c r="D913" t="n">
+        <v>225.54</v>
+      </c>
+      <c r="E913" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="F913" t="n">
+        <v>215.27</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:06+00:00</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>256.03</v>
+      </c>
+      <c r="C914" t="n">
+        <v>225.18</v>
+      </c>
+      <c r="D914" t="n">
+        <v>225.28</v>
+      </c>
+      <c r="E914" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="F914" t="n">
+        <v>214.79</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>257.39</v>
+      </c>
+      <c r="C915" t="n">
+        <v>225.93</v>
+      </c>
+      <c r="D915" t="n">
+        <v>225.55</v>
+      </c>
+      <c r="E915" t="n">
+        <v>216.47</v>
+      </c>
+      <c r="F915" t="n">
+        <v>214.75</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B963"/>
+  <dimension ref="A1:B968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34655,6 +34790,56 @@
       </c>
       <c r="B963" t="n">
         <v>1.79</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -34817,28 +35002,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3102384986398862</v>
+        <v>-0.2915515085394432</v>
       </c>
       <c r="J2" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="K2" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02882078013950951</v>
+        <v>0.025654613259945</v>
       </c>
       <c r="M2" t="n">
-        <v>10.64627027717643</v>
+        <v>10.6737498691717</v>
       </c>
       <c r="N2" t="n">
-        <v>183.6971715732513</v>
+        <v>184.2252414049774</v>
       </c>
       <c r="O2" t="n">
-        <v>13.55349296577275</v>
+        <v>13.57295993528963</v>
       </c>
       <c r="P2" t="n">
-        <v>247.8256214083437</v>
+        <v>247.6335224299428</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34889,28 +35074,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1501012432146078</v>
+        <v>0.1482192501103053</v>
       </c>
       <c r="J3" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="K3" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03371074137440755</v>
+        <v>0.03329896093757079</v>
       </c>
       <c r="M3" t="n">
-        <v>4.560217008574426</v>
+        <v>4.544588225551299</v>
       </c>
       <c r="N3" t="n">
-        <v>36.57841368245414</v>
+        <v>36.39500758482058</v>
       </c>
       <c r="O3" t="n">
-        <v>6.048009067656409</v>
+        <v>6.03282749503254</v>
       </c>
       <c r="P3" t="n">
-        <v>222.9423259125868</v>
+        <v>222.9616672620648</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34961,28 +35146,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4647635909936153</v>
+        <v>0.4656746146240857</v>
       </c>
       <c r="J4" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="K4" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="L4" t="n">
-        <v>0.384234845294895</v>
+        <v>0.3881863335322393</v>
       </c>
       <c r="M4" t="n">
-        <v>3.221960752048453</v>
+        <v>3.208711453835085</v>
       </c>
       <c r="N4" t="n">
-        <v>19.60649664769216</v>
+        <v>19.5036164344898</v>
       </c>
       <c r="O4" t="n">
-        <v>4.427922385012203</v>
+        <v>4.416289894752133</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0581351259285</v>
+        <v>212.0487677960474</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35033,28 +35218,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5766662330244419</v>
+        <v>0.5734816359760632</v>
       </c>
       <c r="J5" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="K5" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5083220285770691</v>
+        <v>0.508178970489874</v>
       </c>
       <c r="M5" t="n">
-        <v>3.451767923400517</v>
+        <v>3.448811353352429</v>
       </c>
       <c r="N5" t="n">
-        <v>18.21831909798826</v>
+        <v>18.16354122146324</v>
       </c>
       <c r="O5" t="n">
-        <v>4.268292292942022</v>
+        <v>4.261870624674479</v>
       </c>
       <c r="P5" t="n">
-        <v>203.5133470563142</v>
+        <v>203.5460793990883</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35105,28 +35290,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5930177995363087</v>
+        <v>0.5918882067265999</v>
       </c>
       <c r="J6" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="K6" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5829693654751763</v>
+        <v>0.585091892127074</v>
       </c>
       <c r="M6" t="n">
-        <v>2.937822911826214</v>
+        <v>2.927573956208424</v>
       </c>
       <c r="N6" t="n">
-        <v>14.24869609672064</v>
+        <v>14.17680294232691</v>
       </c>
       <c r="O6" t="n">
-        <v>3.774744507476055</v>
+        <v>3.765209548262475</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2129884406901</v>
+        <v>200.224601556655</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35164,7 +35349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G910"/>
+  <dimension ref="A1:G915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68837,6 +69022,191 @@
         </is>
       </c>
     </row>
+    <row r="911">
+      <c r="A911" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>-40.947508586033486,173.0500916358074</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>-40.94684809575253,173.04965672435554</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>-40.94614753359734,173.04969319643166</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>-40.94543709505918,173.0497097169806</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>-40.944783628107736,173.04997137420037</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>-40.94750559870055,173.0501255057911</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>-40.9468480948569,173.0496682487783</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>-40.94614833302403,173.0497055073181</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>-40.94543808855108,173.04971780920118</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>-40.944785308332655,173.04997662868502</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>-40.94750549461214,173.05012668592985</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>-40.94684809499548,173.04966646665105</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>-40.946148248469335,173.04970420520507</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>-40.94543811734794,173.0497180437583</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>-40.94478443321553,173.04997389197422</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:06+00:00</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>-40.947506681219565,173.0501132323479</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>-40.946848095097074,173.04966515975775</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>-40.94614804861276,173.04970112748347</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>-40.94543811734794,173.0497180437583</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>-40.944782752990484,173.0499686374897</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>-40.94750526561752,173.0501292822351</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>-40.946848094404025,173.0496740703939</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>-40.94614825615613,173.049704323579</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>-40.94543854930076,173.04972156211517</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>-40.94478261297173,173.04996819961602</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
